--- a/assets/GL_SQL_datas.xlsx
+++ b/assets/GL_SQL_datas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Localisation_Type" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,6 +18,7 @@
     <sheet name="Vecteur_Type" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="SAMU" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="SMUR" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Compétence" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="402">
   <si>
     <t xml:space="preserve">code_start_loc</t>
   </si>
@@ -1169,6 +1170,72 @@
   </si>
   <si>
     <t xml:space="preserve">SMUR_Parthenay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificat de Capacité d'Ambulancier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacité d'Aide Médicale Urgente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formateur de Formateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infirmier de Pratique Avancée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFGSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attestation de Formation aux Gestes et Soins d'Urgence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infirmer Diplômé d'Etat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS6415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réaliser le Transport Sanitaire de Personne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFARM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre de Formation des Assistants de Régulation Médicale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificat d'Exploitant Hospitalier en Télécommunications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant de Régulation Médicale</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1272,6 +1339,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1511,6 +1582,113 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1672,8 +1850,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2361,8 +2539,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2428,8 +2606,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/assets/GL_SQL_datas.xlsx
+++ b/assets/GL_SQL_datas.xlsx
@@ -19,6 +19,7 @@
     <sheet name="SAMU" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="SMUR" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Compétence" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Skill_Job" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="408">
   <si>
     <t xml:space="preserve">code_start_loc</t>
   </si>
@@ -1236,6 +1237,24 @@
   </si>
   <si>
     <t xml:space="preserve">Assistant de Régulation Médicale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résolution conflit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESU Staff</t>
   </si>
 </sst>
 </file>
@@ -1587,95 +1606,329 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="B6" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="B17" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="B18" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="B23" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>401</v>
+      <c r="B25" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/assets/GL_SQL_datas.xlsx
+++ b/assets/GL_SQL_datas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Localisation_Type" sheetId="1" state="visible" r:id="rId3"/>
@@ -19,6 +19,7 @@
     <sheet name="SAMU" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="SMUR" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Compétence" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Profession_TelMed" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="415">
   <si>
     <t xml:space="preserve">code_start_loc</t>
   </si>
@@ -1236,6 +1237,45 @@
   </si>
   <si>
     <t xml:space="preserve">Assistant de Régulation Médicale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generaliste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancerologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dentiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dermatologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gynécologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ophtalmologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pédiatre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urgentiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychiatre</t>
   </si>
 </sst>
 </file>
@@ -1342,8 +1382,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1591,90 +1631,90 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>401</v>
       </c>
     </row>
@@ -1683,8 +1723,92 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>414</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1850,8 +1974,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2539,8 +2663,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2606,8 +2730,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/assets/GL_SQL_datas.xlsx
+++ b/assets/GL_SQL_datas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Localisation_Type" sheetId="1" state="visible" r:id="rId3"/>
@@ -19,7 +19,8 @@
     <sheet name="SAMU" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="SMUR" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Compétence" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Profession_TelMed" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Skill_Job" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Profession_TelMed" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="421">
   <si>
     <t xml:space="preserve">code_start_loc</t>
   </si>
@@ -1237,6 +1238,24 @@
   </si>
   <si>
     <t xml:space="preserve">Assistant de Régulation Médicale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résolution conflit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESU Staff</t>
   </si>
   <si>
     <t xml:space="preserve">profession</t>
@@ -1357,7 +1376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1380,10 +1399,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1627,14 +1642,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>381</v>
       </c>
     </row>
@@ -1694,7 +1709,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>396</v>
       </c>
@@ -1702,7 +1717,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="57.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>398</v>
       </c>
@@ -1716,6 +1731,21 @@
       </c>
       <c r="B11" s="5" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -1723,8 +1753,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1734,72 +1764,207 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="B9" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B10" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B11" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>414</v>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1807,8 +1972,92 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1974,8 +2223,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2663,8 +2912,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2730,8 +2979,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/assets/GL_SQL_datas.xlsx
+++ b/assets/GL_SQL_datas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Localisation_Type" sheetId="1" state="visible" r:id="rId3"/>
@@ -20,6 +20,7 @@
     <sheet name="SMUR" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Compétence" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Skill_Job" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Profession_TelMed" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="421">
   <si>
     <t xml:space="preserve">code_start_loc</t>
   </si>
@@ -1255,6 +1256,45 @@
   </si>
   <si>
     <t xml:space="preserve">CESU Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generaliste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancerologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dentiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dermatologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gynécologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ophtalmologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pédiatre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiologue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urgentiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychiatre</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1358,10 +1398,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1698,17 +1734,17 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>404</v>
       </c>
     </row>
@@ -1732,203 +1768,287 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
